--- a/output/pdf_financials_xlsx/LMR.xlsx
+++ b/output/pdf_financials_xlsx/LMR.xlsx
@@ -5365,34 +5365,34 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.36097</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.408654</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.41043</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.378713</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.420195</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.070639</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.481723</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.320194</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.947824</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.189837</v>
       </c>
     </row>
     <row r="93">
@@ -6644,19 +6644,19 @@
         <v>0.135</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>2.443044</v>
+        <v>2.289804</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.249106</v>
+        <v>-0.353081</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.032514</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.717192</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.721545</v>
       </c>
     </row>
     <row r="119">
@@ -8688,7 +8688,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9746,7 +9750,11 @@
           <t>Reserves(Note 7)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11020,7 +11028,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12354,7 +12366,11 @@
           <t>Share based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13288,7 +13304,11 @@
           <t>Share based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -14316,7 +14336,11 @@
           <t>Share based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -17626,7 +17650,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -19876,7 +19904,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LMR.xlsx
+++ b/output/pdf_financials_xlsx/LMR.xlsx
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001291</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -954,25 +954,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.013045</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.023834</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>2.1e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
         <v>-1.185199</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.833491</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.744268</v>
@@ -1757,25 +1757,25 @@
         <v>-0.601737</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.816627</v>
+        <v>-0.829672</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.176967</v>
+        <v>1.153133</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.688471</v>
+        <v>-2.689971</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.944034</v>
+        <v>-0.9440499999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.525606</v>
+        <v>-5.525627</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.760938</v>
+        <v>-1.760957</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.186004</v>
+        <v>-1.186022</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.735706</v>
@@ -1843,7 +1843,7 @@
         <v>-1.185199</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.833491</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.744268</v>
@@ -1855,25 +1855,25 @@
         <v>-0.601737</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.816627</v>
+        <v>-0.829672</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.176967</v>
+        <v>1.153133</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.688471</v>
+        <v>-2.689971</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.944034</v>
+        <v>-0.9440499999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.525606</v>
+        <v>-5.525627</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.760938</v>
+        <v>-1.760957</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.186004</v>
+        <v>-1.186022</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.735706</v>
@@ -31508,7 +31508,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -35068,7 +35068,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -38212,7 +38212,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -39938,7 +39938,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -40026,7 +40026,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
